--- a/data/datasets/test_reports/PCRTA/PCRTA_of_feature_group_1.xlsx
+++ b/data/datasets/test_reports/PCRTA/PCRTA_of_feature_group_1.xlsx
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.420371564626262</v>
+        <v>2.420371542274187</v>
       </c>
       <c r="D2" t="n">
-        <v>1.428125593505512</v>
+        <v>1.428125633420372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007962135760019029</v>
+        <v>0.0007962136838692846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04112458159630128</v>
+        <v>0.04112457755552845</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.842483301559812</v>
+        <v>1.842483299625432</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7286289892769761</v>
+        <v>0.7286290076881842</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01199103703347459</v>
+        <v>0.01199103711605298</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1500013035828334</v>
+        <v>0.1500012998311042</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.482781343428548</v>
+        <v>1.482781335435039</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.697821680170077</v>
+        <v>-1.697821007560447</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03582992277704433</v>
+        <v>0.03582992351674574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6687379727792873</v>
+        <v>0.668737868008506</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.625486870741028</v>
+        <v>1.625486868367021</v>
       </c>
       <c r="D5" t="n">
-        <v>1.666982991374693</v>
+        <v>1.666983002647229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02419091899843018</v>
+        <v>0.024190919166721</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02137242908872261</v>
+        <v>0.02137242835612618</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.246974478181886</v>
+        <v>2.246974446285106</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08312315073730742</v>
+        <v>0.08312322583305226</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002101071285203648</v>
+        <v>0.0021010716308002</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2972089583307296</v>
+        <v>0.2972089401920051</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.363218367392724</v>
+        <v>1.363218396048124</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7226277718815441</v>
+        <v>-0.7226279842868858</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04803523037326751</v>
+        <v>0.04803522717171405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4859528393691463</v>
+        <v>0.4859528856860303</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-3.248675147088785</v>
+        <v>-3.248673094342911</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.15177622860459</v>
+        <v>-1.151775802423691</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8437945471859061</v>
+        <v>0.8437943889249633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5739761205504861</v>
+        <v>0.5739760389365605</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.303245001004526</v>
+        <v>-1.30324501772087</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7635000180609377</v>
+        <v>-0.7635004557853737</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6022278414430395</v>
+        <v>0.6022278444774023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4948181133160519</v>
+        <v>0.4948182077485002</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -776,16 +776,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.1362924546879116</v>
+        <v>-0.1362926624948801</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1670967600467915</v>
+        <v>0.1670972357770013</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3502400007192445</v>
+        <v>0.350240050779688</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2769759102817659</v>
+        <v>0.2769757960160678</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-2.521446984944497</v>
+        <v>-2.521447479927384</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.417389410441209</v>
+        <v>-3.417389257527109</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7768327638344712</v>
+        <v>0.7768328176030586</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8562874912846935</v>
+        <v>0.8562874804164603</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-3.064741073468313</v>
+        <v>-3.064743716313878</v>
       </c>
       <c r="D12" t="n">
-        <v>1.044260878470237</v>
+        <v>1.044260188352037</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8289698431943174</v>
+        <v>0.8289700657036</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0918699921850189</v>
+        <v>0.09187010428669373</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2881591080704584</v>
+        <v>0.2881588469250984</v>
       </c>
       <c r="D13" t="n">
-        <v>1.470100562647337</v>
+        <v>1.470100559912431</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2481002597130488</v>
+        <v>0.2481003214716627</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03701606299686444</v>
+        <v>0.0370160632554245</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
